--- a/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51493204-7CAC-4CC9-8EDA-56FDAF6AE9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB58BCC-4DF6-4829-B021-56F8BBAE221A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6390" yWindow="-12675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6900" yWindow="3600" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -380,53 +380,54 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="23.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="str">
-        <f>C2&amp;"秒間の間 "&amp;D2&amp;"秒間毎に"</f>
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>0.3</v>
+      </c>
+      <c r="D2" t="str">
+        <f>B2&amp;"秒間の間 "&amp;C2&amp;"秒間毎に"</f>
         <v>3秒間の間 0.3秒間毎に</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>0.3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="str">
-        <f>C3&amp;"秒間の間 "&amp;D3&amp;"秒間毎に"</f>
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>0.5</v>
+      </c>
+      <c r="D3" t="str">
+        <f>B3&amp;"秒間の間 "&amp;C3&amp;"秒間毎に"</f>
         <v>3秒間の間 0.5秒間毎に</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB58BCC-4DF6-4829-B021-56F8BBAE221A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18FCB34-D028-46CD-9782-A35750D6D6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6900" yWindow="3600" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6810" yWindow="2130" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>comment</t>
     <phoneticPr fontId="1"/>
@@ -52,6 +52,10 @@
   </si>
   <si>
     <t>intervalSecond</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>firstInterval</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -377,16 +381,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -397,10 +401,13 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -410,12 +417,15 @@
       <c r="C2">
         <v>0.3</v>
       </c>
-      <c r="D2" t="str">
-        <f>B2&amp;"秒間の間 "&amp;C2&amp;"秒間毎に"</f>
-        <v>3秒間の間 0.3秒間毎に</v>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="str">
+        <f>D2&amp;"秒後,"&amp;B2&amp;"秒間の間, "&amp;C2&amp;"秒間毎に"</f>
+        <v>0秒後,3秒間の間, 0.3秒間毎に</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -425,9 +435,30 @@
       <c r="C3">
         <v>0.5</v>
       </c>
-      <c r="D3" t="str">
-        <f>B3&amp;"秒間の間 "&amp;C3&amp;"秒間毎に"</f>
-        <v>3秒間の間 0.5秒間毎に</v>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="str">
+        <f>D3&amp;"秒後,"&amp;B3&amp;"秒間の間, "&amp;C3&amp;"秒間毎に"</f>
+        <v>0秒後,3秒間の間, 0.5秒間毎に</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>-1</v>
+      </c>
+      <c r="C4">
+        <v>0.2</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="str">
+        <f>D4&amp;"秒後,"&amp;B4&amp;"秒間の間, "&amp;C4&amp;"秒間毎に"</f>
+        <v>0.5秒後,-1秒間の間, 0.2秒間毎に</v>
       </c>
     </row>
   </sheetData>

--- a/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18FCB34-D028-46CD-9782-A35750D6D6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0A17BC-6516-4531-8AC2-43F2E992869C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6810" yWindow="2130" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -451,14 +448,14 @@
         <v>-1</v>
       </c>
       <c r="C4">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
       <c r="E4" t="str">
         <f>D4&amp;"秒後,"&amp;B4&amp;"秒間の間, "&amp;C4&amp;"秒間毎に"</f>
-        <v>0.5秒後,-1秒間の間, 0.2秒間毎に</v>
+        <v>0.5秒後,-1秒間の間, 0.05秒間毎に</v>
       </c>
     </row>
   </sheetData>

--- a/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0A17BC-6516-4531-8AC2-43F2E992869C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71715585-32E8-4BCA-B111-D1D9AF3F4D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -451,11 +454,11 @@
         <v>0.05</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="str">
         <f>D4&amp;"秒後,"&amp;B4&amp;"秒間の間, "&amp;C4&amp;"秒間毎に"</f>
-        <v>0.5秒後,-1秒間の間, 0.05秒間毎に</v>
+        <v>0.4秒後,-1秒間の間, 0.05秒間毎に</v>
       </c>
     </row>
   </sheetData>
